--- a/review/etnografiya/may-december/accepted/january/january.xlsx
+++ b/review/etnografiya/may-december/accepted/january/january.xlsx
@@ -108,7 +108,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как на домашней ёлке встретились дореволюционный ангел и советская ракета?</t>
+          <t xml:space="preserve">На одной домашней ёлке соседствуют ангел и ракета. Маленькие игрушки сохраняют следы больших перемен в жизни русской семьи.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -135,7 +135,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">До скотного двора можно дойти, не выходя под снег. Как жила семья в таком доме?</t>
+          <t xml:space="preserve">Семья идёт к скотному двору, не выходя под снег. Северный дом собирает жильё и хозяйство под одной крышей — мороз меняет сам план жизни.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -162,7 +162,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">У этого цветка горели три бутона. Зачем под него ставили корыто с водой?</t>
+          <t xml:space="preserve">У железного цветка горят три бутона-лучины. Корыто с водой внизу выдаёт цену домашнего света: за каждым огоньком приходилось следить.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Горшок раскалён, а ручек нет. Как поставить ужин на стол?</t>
+          <t xml:space="preserve">Горшок раскалён, а ручек нет. Железная рогатина ухвата позволяет достать ужин из глубины печи — работа держится на точном движении рук.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -216,7 +216,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ни подошвы, ни шва — а получился сапог. Что сделали с обычной шерстью?</t>
+          <t xml:space="preserve">Ни подошвы, ни шва — а получился сапог. Мастер уплотняет шерсть в валенок: мягкие волокна становятся защитой от русского зимнего холода.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -243,7 +243,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">До Рождества — одна ночь. Почему праздничный стол ещё остаётся постным?</t>
+          <t xml:space="preserve">До Рождества одна ночь, а стол ещё постный. Сочельник отделяет ожидание от праздника — семейная трапеза хранит этот переход.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -270,7 +270,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Звезда была не только на ёлке: с ней стучались в соседские двери. Зачем?</t>
+          <t xml:space="preserve">Рождественскую звезду несут от дома к дому. Праздник выходит за семейный стол: соседскую дверь открывают песне и доброму пожеланию.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -297,7 +297,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">После Рождества чествовали женщину, которая помогла тебе появиться на свет. Чем её благодарили?</t>
+          <t xml:space="preserve">После Рождества благодарят женщину, помогавшую детям появиться на свет. За праздничным обычаем стоит труд повивальной бабки.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">За пожелание доброго года открывали дверь и давали угощение. Что связывало хозяев и певцов?</t>
+          <t xml:space="preserve">Певцы приносят пожелание доброго года, хозяева отвечают угощением. Святки превращают соседскую дверь в место взаимного дара.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -351,7 +351,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рождественское пожелание в Архангельске можно было подарить в виде пряника?</t>
+          <t xml:space="preserve">Рождественское пожелание можно испечь и подарить. Архангельская козуля соединяет пряничное ремесло, праздничный образ и тепло рук.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -378,7 +378,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бархатное сиденье, бахрома, меховой полог. Зачем саням столько наряда?</t>
+          <t xml:space="preserve">Бархат, бахрома и мех едут по снегу. Нарядные сани превращают зимнюю дорогу в выход на люди — мастерство видно ещё до остановки.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -405,7 +405,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кумачовая рубаха, жилет и картуз: что выдавало деревенского модника?</t>
+          <t xml:space="preserve">Кумачовая рубаха, жилет и картуз собираются в праздничный образ. Деревенский наряд хранит собственный язык щегольства и достоинства.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -432,7 +432,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кольцо вытаскивают наугад, а смысл даёт песня. О чём девушки хотели узнать?</t>
+          <t xml:space="preserve">Кольцо достают наугад, а толкование задаёт песня. Подблюдное гадание сохраняет девичьи ожидания будущего, а не знание о грядущем.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -459,7 +459,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">На улице снег, а зерно разбрасывают прямо в доме. Какого урожая здесь ждут?</t>
+          <t xml:space="preserve">За окном снег, а в доме разбрасывают зерно. Зимнее пожелание урожая переносит заботу о будущем поле прямо к семейному порогу.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тулуп вывернут, лицо скрыто. Почему знакомый человек должен был стать неузнаваемым?</t>
+          <t xml:space="preserve">Тулуп вывернут, лицо скрыто — соседа трудно узнать. Ряженье позволяет знакомому человеку ненадолго войти в праздничную чужую роль.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Драгоценный венец — у деревенской девушки. Как его делали и когда надевали?</t>
+          <t xml:space="preserve">Деревенская девушка надевает нарядный венец. В маленьких деталях убора соединяются мастерство рук и торжественность выхода на люди.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">За бревенчатыми стенами — парадная зала. Как деревенская семья показывала связь с Петербургом?</t>
+          <t xml:space="preserve">За бревенчатыми стенами открывается парадная зала. Северный дом хранит городской след: связь с Петербургом читается в его интерьере.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крест, ковш и ведро встретились на одной выставке. Что связывает их с зимним праздником?</t>
+          <t xml:space="preserve">Крест, ковш и ведро оказываются рядом. Крещенский праздник связывает церковный обряд с простыми вещами, которыми набирали и хранили воду.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему зимняя прорубь получила имя далёкой реки?</t>
+          <t xml:space="preserve">Зимнюю прорубь называют Иорданью. Имя далёкой реки входит в русский зимний пейзаж через память о Крещении и местный праздничный обряд.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Семья пьёт чай, рядом колокольня и двуглавый орёл. Зачем всё это вырезали на прялке?</t>
+          <t xml:space="preserve">На прялке вырезаны чаепитие, колокольня и двуглавый орёл. Рабочая вещь становится маленькой картиной мира, оставленной мастером.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Прялка стоит неподвижно. Что же на самом деле превращает волокно в нить?</t>
+          <t xml:space="preserve">Прялка удерживает волокно, а веретено скручивает нить. За привычным названием скрыта работа двух разных предметов и умелых пальцев.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Эта ребристая доска не стирает. Как она расправляет жёсткое бельё?</t>
+          <t xml:space="preserve">Ребристая доска расправляет бельё без горячей подошвы. Рубель работает вместе с валиком: тяжёлый домашний труд превращён в точный приём.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Поднял дощечку, опустил — и нити поменялись местами. Как из этого получается пояс?</t>
+          <t xml:space="preserve">Дощечка поднимается — нити меняются местами. В узком поясе остаётся порядок движений ткачихи: рисунок рождается из переплетения.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Перед нами русские женские наряды — а привычного сарафана нет. Что рассказывает клетчатая понёва?</t>
+          <t xml:space="preserve">Перед нами русский женский наряд без сарафана. Клетчатая понёва открывает другой крой и местную традицию, которую нельзя свести к одной картинке.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Университетский праздник вышел на московские улицы. Что делало чужих людей «старыми студентами»?</t>
+          <t xml:space="preserve">Университетский праздник выходит на московские улицы. Встреча «старых студентов» связывает людей, чьи годы учёбы давно остались позади.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вода окружает огонь, но не гасит его. Что спрятано внутри самовара?</t>
+          <t xml:space="preserve">Вода окружает огонь, но не гасит его. Внутри самовара проходит жаровая труба — семейное чаепитие начинается с продуманного устройства.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кору сняли летом, а зимой из неё делают домашнюю утварь. Как ленты держатся без ткани?</t>
+          <t xml:space="preserve">Берестяные ленты переплетаются без нитки и ткани. Снятая летом кора становится домашней утварью: гибкость материала работает на мастера.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Несколько зарубок — и в куске дерева уже виден конь. Как мастер замечает его раньше нас?</t>
+          <t xml:space="preserve">Несколько зарубок — и в дереве проступает конь. Мастер убирает лишнее так, что маленькая игрушка сохраняет узнаваемый характер животного.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дом можно перевезти только по брёвнышку. А как переселенцы увезли с собой общий голос?</t>
+          <t xml:space="preserve">Дом перевозят по брёвнышку, а песню уносят в памяти. Общий голос помогает переселенцам сохранять связь с оставленной родиной.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Снаружи мороз, а на сундуке цветут яркие букеты. Как роспись меняла домашний мир?</t>
+          <t xml:space="preserve">Снаружи мороз, на сундуке цветут букеты. Роспись превращает место хранения вещей в яркий домашний мир, созданный человеческими руками.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">За месяц мы разобрали столько вещей. Сможешь теперь увидеть труд за обычной полоской ткани?</t>
+          <t xml:space="preserve">За полоской ткани скрываются прядение, ткачество и отделка. Обычная вещь становится видимой цепочкой труда — от волокна до семейного дома.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
